--- a/appium-android-report.xlsx
+++ b/appium-android-report.xlsx
@@ -31,10 +31,10 @@
     <t>Timestamp</t>
   </si>
   <si>
-    <t>UI/UX Testing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC001: Verify consistency of font styles across Mobile screens </t>
+    <t>Mobile UI/UX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC001: Verify touch target sizes </t>
   </si>
   <si>
     <t>PASS</t>
@@ -43,916 +43,916 @@
     <t/>
   </si>
   <si>
-    <t>8/7/2026, 3:55:25 AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC002: Verify color contrast for readability in dark mode </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC003: Verify button hover effects and animations </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC004: Verify clear error messages for invalid inputs </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC005: Verify smooth transitions between dashboard tabs </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC006: Verify image loading placeholders for menu items </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC007: Verify form field alignment on checkout page </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC008: Verify dark mode UI consistency </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC009: Verify glassmorphism effect on cards </t>
-  </si>
-  <si>
-    <t>TC010: Verify consistency of font styles across Mobile screens (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC011: Verify color contrast for readability in dark mode (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC012: Verify button hover effects and animations (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC013: Verify clear error messages for invalid inputs (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC014: Verify smooth transitions between dashboard tabs (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC015: Verify image loading placeholders for menu items (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC016: Verify form field alignment on checkout page (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC017: Verify dark mode UI consistency (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC018: Verify glassmorphism effect on cards (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC019: Verify consistency of font styles across Mobile screens (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC020: Verify color contrast for readability in dark mode (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC021: Verify button hover effects and animations (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC022: Verify clear error messages for invalid inputs (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC023: Verify smooth transitions between dashboard tabs (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC024: Verify image loading placeholders for menu items (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC025: Verify form field alignment on checkout page (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC026: Verify dark mode UI consistency (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC027: Verify glassmorphism effect on cards (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC028: Verify consistency of font styles across Mobile screens (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC029: Verify color contrast for readability in dark mode (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC030: Verify button hover effects and animations (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC031: Verify clear error messages for invalid inputs (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC032: Verify smooth transitions between dashboard tabs (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC033: Verify image loading placeholders for menu items (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC034: Verify form field alignment on checkout page (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC035: Verify dark mode UI consistency (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC036: Verify glassmorphism effect on cards (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC037: Verify consistency of font styles across Mobile screens (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC038: Verify color contrast for readability in dark mode (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC039: Verify button hover effects and animations (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC040: Verify clear error messages for invalid inputs (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC041: Verify smooth transitions between dashboard tabs (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC042: Verify image loading placeholders for menu items (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC043: Verify form field alignment on checkout page (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC044: Verify dark mode UI consistency (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC045: Verify glassmorphism effect on cards (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC046: Verify consistency of font styles across Mobile screens (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC047: Verify color contrast for readability in dark mode (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC048: Verify button hover effects and animations (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC049: Verify clear error messages for invalid inputs (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC050: Verify smooth transitions between dashboard tabs (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC051: Verify image loading placeholders for menu items (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC052: Verify form field alignment on checkout page (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC053: Verify dark mode UI consistency (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC054: Verify glassmorphism effect on cards (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC055: Verify consistency of font styles across Mobile screens (Variation 7)</t>
-  </si>
-  <si>
-    <t>TC056: Verify color contrast for readability in dark mode (Variation 7)</t>
-  </si>
-  <si>
-    <t>TC057: Verify button hover effects and animations (Variation 7)</t>
-  </si>
-  <si>
-    <t>TC058: Verify clear error messages for invalid inputs (Variation 7)</t>
-  </si>
-  <si>
-    <t>TC059: Verify smooth transitions between dashboard tabs (Variation 7)</t>
-  </si>
-  <si>
-    <t>TC060: Verify image loading placeholders for menu items (Variation 7)</t>
-  </si>
-  <si>
-    <t>Compatibility Testing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC061: Verify app behavior on small screens </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC062: Verify app behavior on tablets/large screens </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC063: Verify app compatibility with latest OS version </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC064: Verify app compatibility with older OS versions </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC065: Verify app behavior on different aspect ratios </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC066: Verify app fonts scaling with system settings </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC067: Verify background tasks on low-end hardware </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC068: Verify app launch time on cold start </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC069: Verify interaction with system navigation gestures </t>
-  </si>
-  <si>
-    <t>TC070: Verify app behavior on small screens (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC071: Verify app behavior on tablets/large screens (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC072: Verify app compatibility with latest OS version (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC073: Verify app compatibility with older OS versions (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC074: Verify app behavior on different aspect ratios (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC075: Verify app fonts scaling with system settings (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC076: Verify background tasks on low-end hardware (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC077: Verify app launch time on cold start (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC078: Verify interaction with system navigation gestures (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC079: Verify app behavior on small screens (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC080: Verify app behavior on tablets/large screens (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC081: Verify app compatibility with latest OS version (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC082: Verify app compatibility with older OS versions (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC083: Verify app behavior on different aspect ratios (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC084: Verify app fonts scaling with system settings (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC085: Verify background tasks on low-end hardware (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC086: Verify app launch time on cold start (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC087: Verify interaction with system navigation gestures (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC088: Verify app behavior on small screens (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC089: Verify app behavior on tablets/large screens (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC090: Verify app compatibility with latest OS version (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC091: Verify app compatibility with older OS versions (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC092: Verify app behavior on different aspect ratios (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC093: Verify app fonts scaling with system settings (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC094: Verify background tasks on low-end hardware (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC095: Verify app launch time on cold start (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC096: Verify interaction with system navigation gestures (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC097: Verify app behavior on small screens (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC098: Verify app behavior on tablets/large screens (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC099: Verify app compatibility with latest OS version (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC100: Verify app compatibility with older OS versions (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC101: Verify app behavior on different aspect ratios (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC102: Verify app fonts scaling with system settings (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC103: Verify background tasks on low-end hardware (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC104: Verify app launch time on cold start (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC105: Verify interaction with system navigation gestures (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC106: Verify app behavior on small screens (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC107: Verify app behavior on tablets/large screens (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC108: Verify app compatibility with latest OS version (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC109: Verify app compatibility with older OS versions (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC110: Verify app behavior on different aspect ratios (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC111: Verify app fonts scaling with system settings (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC112: Verify background tasks on low-end hardware (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC113: Verify app launch time on cold start (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC114: Verify interaction with system navigation gestures (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC115: Verify app behavior on small screens (Variation 7)</t>
-  </si>
-  <si>
-    <t>TC116: Verify app behavior on tablets/large screens (Variation 7)</t>
-  </si>
-  <si>
-    <t>TC117: Verify app compatibility with latest OS version (Variation 7)</t>
-  </si>
-  <si>
-    <t>TC118: Verify app compatibility with older OS versions (Variation 7)</t>
-  </si>
-  <si>
-    <t>TC119: Verify app behavior on different aspect ratios (Variation 7)</t>
-  </si>
-  <si>
-    <t>TC120: Verify app fonts scaling with system settings (Variation 7)</t>
-  </si>
-  <si>
-    <t>Accessibility Testing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC121: Verify screen reader support for all flows </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC122: Verify touch target sizes meet standards </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC123: Verify high contrast theme support </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC124: Verify text scaling without layout breakage </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC125: Verify descriptive alt text for images </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC126: Verify focus indicators for interactive elements </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC127: Verify keyboard navigation support </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC128: Verify captions for any video content </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC129: Verify clear error announcements to screen reader </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC130: Verify accessible names for icons </t>
-  </si>
-  <si>
-    <t>TC131: Verify screen reader support for all flows (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC132: Verify touch target sizes meet standards (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC133: Verify high contrast theme support (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC134: Verify text scaling without layout breakage (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC135: Verify descriptive alt text for images (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC136: Verify focus indicators for interactive elements (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC137: Verify keyboard navigation support (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC138: Verify captions for any video content (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC139: Verify clear error announcements to screen reader (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC140: Verify accessible names for icons (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC141: Verify screen reader support for all flows (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC142: Verify touch target sizes meet standards (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC143: Verify high contrast theme support (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC144: Verify text scaling without layout breakage (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC145: Verify descriptive alt text for images (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC146: Verify focus indicators for interactive elements (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC147: Verify keyboard navigation support (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC148: Verify captions for any video content (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC149: Verify clear error announcements to screen reader (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC150: Verify accessible names for icons (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC151: Verify screen reader support for all flows (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC152: Verify touch target sizes meet standards (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC153: Verify high contrast theme support (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC154: Verify text scaling without layout breakage (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC155: Verify descriptive alt text for images (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC156: Verify focus indicators for interactive elements (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC157: Verify keyboard navigation support (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC158: Verify captions for any video content (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC159: Verify clear error announcements to screen reader (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC160: Verify accessible names for icons (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC161: Verify screen reader support for all flows (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC162: Verify touch target sizes meet standards (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC163: Verify high contrast theme support (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC164: Verify text scaling without layout breakage (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC165: Verify descriptive alt text for images (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC166: Verify focus indicators for interactive elements (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC167: Verify keyboard navigation support (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC168: Verify captions for any video content (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC169: Verify clear error announcements to screen reader (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC170: Verify accessible names for icons (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC171: Verify screen reader support for all flows (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC172: Verify touch target sizes meet standards (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC173: Verify high contrast theme support (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC174: Verify text scaling without layout breakage (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC175: Verify descriptive alt text for images (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC176: Verify focus indicators for interactive elements (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC177: Verify keyboard navigation support (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC178: Verify captions for any video content (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC179: Verify clear error announcements to screen reader (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC180: Verify accessible names for icons (Variation 6)</t>
-  </si>
-  <si>
-    <t>Platform-Specific Testing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC181: Verify app behavior on incoming calls </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC182: Verify app behavior during network switch </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC183: Verify push notification click-through behavior </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC184: Verify app state preservation during backgrounding </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC185: Verify camera integration for profile picture </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC186: Verify location permission handling </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC187: Verify deep link processing </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC188: Verify orientation change handling </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC189: Verify offline data sync functionality </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC190: Verify app interaction with other system apps </t>
-  </si>
-  <si>
-    <t>TC191: Verify app behavior on incoming calls (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC192: Verify app behavior during network switch (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC193: Verify push notification click-through behavior (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC194: Verify app state preservation during backgrounding (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC195: Verify camera integration for profile picture (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC196: Verify location permission handling (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC197: Verify deep link processing (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC198: Verify orientation change handling (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC199: Verify offline data sync functionality (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC200: Verify app interaction with other system apps (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC201: Verify app behavior on incoming calls (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC202: Verify app behavior during network switch (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC203: Verify push notification click-through behavior (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC204: Verify app state preservation during backgrounding (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC205: Verify camera integration for profile picture (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC206: Verify location permission handling (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC207: Verify deep link processing (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC208: Verify orientation change handling (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC209: Verify offline data sync functionality (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC210: Verify app interaction with other system apps (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC211: Verify app behavior on incoming calls (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC212: Verify app behavior during network switch (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC213: Verify push notification click-through behavior (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC214: Verify app state preservation during backgrounding (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC215: Verify camera integration for profile picture (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC216: Verify location permission handling (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC217: Verify deep link processing (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC218: Verify orientation change handling (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC219: Verify offline data sync functionality (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC220: Verify app interaction with other system apps (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC221: Verify app behavior on incoming calls (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC222: Verify app behavior during network switch (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC223: Verify push notification click-through behavior (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC224: Verify app state preservation during backgrounding (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC225: Verify camera integration for profile picture (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC226: Verify location permission handling (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC227: Verify deep link processing (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC228: Verify orientation change handling (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC229: Verify offline data sync functionality (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC230: Verify app interaction with other system apps (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC231: Verify app behavior on incoming calls (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC232: Verify app behavior during network switch (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC233: Verify push notification click-through behavior (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC234: Verify app state preservation during backgrounding (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC235: Verify camera integration for profile picture (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC236: Verify location permission handling (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC237: Verify deep link processing (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC238: Verify orientation change handling (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC239: Verify offline data sync functionality (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC240: Verify app interaction with other system apps (Variation 6)</t>
-  </si>
-  <si>
-    <t>End-to-End Testing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC241: Full Flow: User login, add to cart, and checkout </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC242: Full Flow: Admin dashboard monitoring to order approval </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC243: Full Flow: Guest search to login prompt to ordering </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC244: Full Flow: Payment gateway processing and confirmation </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC245: Full Flow: Order status tracking from placed to delivered </t>
-  </si>
-  <si>
-    <t>TC246: Full Flow: User login, add to cart, and checkout (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC247: Full Flow: Admin dashboard monitoring to order approval (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC248: Full Flow: Guest search to login prompt to ordering (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC249: Full Flow: Payment gateway processing and confirmation (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC250: Full Flow: Order status tracking from placed to delivered (Variation 2)</t>
-  </si>
-  <si>
-    <t>TC251: Full Flow: User login, add to cart, and checkout (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC252: Full Flow: Admin dashboard monitoring to order approval (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC253: Full Flow: Guest search to login prompt to ordering (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC254: Full Flow: Payment gateway processing and confirmation (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC255: Full Flow: Order status tracking from placed to delivered (Variation 3)</t>
-  </si>
-  <si>
-    <t>TC256: Full Flow: User login, add to cart, and checkout (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC257: Full Flow: Admin dashboard monitoring to order approval (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC258: Full Flow: Guest search to login prompt to ordering (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC259: Full Flow: Payment gateway processing and confirmation (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC260: Full Flow: Order status tracking from placed to delivered (Variation 4)</t>
-  </si>
-  <si>
-    <t>TC261: Full Flow: User login, add to cart, and checkout (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC262: Full Flow: Admin dashboard monitoring to order approval (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC263: Full Flow: Guest search to login prompt to ordering (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC264: Full Flow: Payment gateway processing and confirmation (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC265: Full Flow: Order status tracking from placed to delivered (Variation 5)</t>
-  </si>
-  <si>
-    <t>TC266: Full Flow: User login, add to cart, and checkout (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC267: Full Flow: Admin dashboard monitoring to order approval (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC268: Full Flow: Guest search to login prompt to ordering (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC269: Full Flow: Payment gateway processing and confirmation (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC270: Full Flow: Order status tracking from placed to delivered (Variation 6)</t>
-  </si>
-  <si>
-    <t>TC271: Full Flow: User login, add to cart, and checkout (Variation 7)</t>
-  </si>
-  <si>
-    <t>TC272: Full Flow: Admin dashboard monitoring to order approval (Variation 7)</t>
-  </si>
-  <si>
-    <t>TC273: Full Flow: Guest search to login prompt to ordering (Variation 7)</t>
-  </si>
-  <si>
-    <t>TC274: Full Flow: Payment gateway processing and confirmation (Variation 7)</t>
-  </si>
-  <si>
-    <t>TC275: Full Flow: Order status tracking from placed to delivered (Variation 7)</t>
-  </si>
-  <si>
-    <t>TC276: Full Flow: User login, add to cart, and checkout (Variation 8)</t>
-  </si>
-  <si>
-    <t>TC277: Full Flow: Admin dashboard monitoring to order approval (Variation 8)</t>
-  </si>
-  <si>
-    <t>TC278: Full Flow: Guest search to login prompt to ordering (Variation 8)</t>
-  </si>
-  <si>
-    <t>TC279: Full Flow: Payment gateway processing and confirmation (Variation 8)</t>
-  </si>
-  <si>
-    <t>TC280: Full Flow: Order status tracking from placed to delivered (Variation 8)</t>
-  </si>
-  <si>
-    <t>TC281: Full Flow: User login, add to cart, and checkout (Variation 9)</t>
-  </si>
-  <si>
-    <t>TC282: Full Flow: Admin dashboard monitoring to order approval (Variation 9)</t>
-  </si>
-  <si>
-    <t>TC283: Full Flow: Guest search to login prompt to ordering (Variation 9)</t>
-  </si>
-  <si>
-    <t>TC284: Full Flow: Payment gateway processing and confirmation (Variation 9)</t>
-  </si>
-  <si>
-    <t>TC285: Full Flow: Order status tracking from placed to delivered (Variation 9)</t>
-  </si>
-  <si>
-    <t>TC286: Full Flow: User login, add to cart, and checkout (Variation 10)</t>
-  </si>
-  <si>
-    <t>TC287: Full Flow: Admin dashboard monitoring to order approval (Variation 10)</t>
-  </si>
-  <si>
-    <t>TC288: Full Flow: Guest search to login prompt to ordering (Variation 10)</t>
-  </si>
-  <si>
-    <t>TC289: Full Flow: Payment gateway processing and confirmation (Variation 10)</t>
-  </si>
-  <si>
-    <t>TC290: Full Flow: Order status tracking from placed to delivered (Variation 10)</t>
-  </si>
-  <si>
-    <t>TC291: Full Flow: User login, add to cart, and checkout (Variation 11)</t>
-  </si>
-  <si>
-    <t>TC292: Full Flow: Admin dashboard monitoring to order approval (Variation 11)</t>
-  </si>
-  <si>
-    <t>TC293: Full Flow: Guest search to login prompt to ordering (Variation 11)</t>
-  </si>
-  <si>
-    <t>TC294: Full Flow: Payment gateway processing and confirmation (Variation 11)</t>
-  </si>
-  <si>
-    <t>TC295: Full Flow: Order status tracking from placed to delivered (Variation 11)</t>
-  </si>
-  <si>
-    <t>TC296: Full Flow: User login, add to cart, and checkout (Variation 12)</t>
-  </si>
-  <si>
-    <t>TC297: Full Flow: Admin dashboard monitoring to order approval (Variation 12)</t>
-  </si>
-  <si>
-    <t>TC298: Full Flow: Guest search to login prompt to ordering (Variation 12)</t>
-  </si>
-  <si>
-    <t>TC299: Full Flow: Payment gateway processing and confirmation (Variation 12)</t>
-  </si>
-  <si>
-    <t>TC300: Full Flow: Order status tracking from placed to delivered (Variation 12)</t>
+    <t>8/7/2026, 4:01:40 AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC002: Verify bottom navigation bar </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC003: Verify gesture controls </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC004: Verify dark mode UI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC005: Verify splash screen animations </t>
+  </si>
+  <si>
+    <t>TC006: Verify touch target sizes (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC007: Verify bottom navigation bar (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC008: Verify gesture controls (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC009: Verify dark mode UI (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC010: Verify splash screen animations (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC011: Verify touch target sizes (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC012: Verify bottom navigation bar (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC013: Verify gesture controls (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC014: Verify dark mode UI (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC015: Verify splash screen animations (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC016: Verify touch target sizes (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC017: Verify bottom navigation bar (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC018: Verify gesture controls (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC019: Verify dark mode UI (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC020: Verify splash screen animations (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC021: Verify touch target sizes (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC022: Verify bottom navigation bar (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC023: Verify gesture controls (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC024: Verify dark mode UI (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC025: Verify splash screen animations (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC026: Verify touch target sizes (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC027: Verify bottom navigation bar (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC028: Verify gesture controls (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC029: Verify dark mode UI (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC030: Verify splash screen animations (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC031: Verify touch target sizes (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC032: Verify bottom navigation bar (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC033: Verify gesture controls (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC034: Verify dark mode UI (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC035: Verify splash screen animations (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC036: Verify touch target sizes (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC037: Verify bottom navigation bar (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC038: Verify gesture controls (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC039: Verify dark mode UI (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC040: Verify splash screen animations (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC041: Verify touch target sizes (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC042: Verify bottom navigation bar (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC043: Verify gesture controls (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC044: Verify dark mode UI (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC045: Verify splash screen animations (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC046: Verify touch target sizes (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC047: Verify bottom navigation bar (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC048: Verify gesture controls (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC049: Verify dark mode UI (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC050: Verify splash screen animations (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC051: Verify touch target sizes (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC052: Verify bottom navigation bar (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC053: Verify gesture controls (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC054: Verify dark mode UI (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC055: Verify splash screen animations (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC056: Verify touch target sizes (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC057: Verify bottom navigation bar (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC058: Verify gesture controls (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC059: Verify dark mode UI (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC060: Verify splash screen animations (Scenario 12)</t>
+  </si>
+  <si>
+    <t>Android Compatibility</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC061: Verify app on Android 11 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC062: Verify app on Android 13 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC063: Verify app on small screen device </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC064: Verify split-screen mode </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC065: Verify orientation lock </t>
+  </si>
+  <si>
+    <t>TC066: Verify app on Android 11 (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC067: Verify app on Android 13 (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC068: Verify app on small screen device (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC069: Verify split-screen mode (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC070: Verify orientation lock (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC071: Verify app on Android 11 (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC072: Verify app on Android 13 (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC073: Verify app on small screen device (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC074: Verify split-screen mode (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC075: Verify orientation lock (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC076: Verify app on Android 11 (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC077: Verify app on Android 13 (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC078: Verify app on small screen device (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC079: Verify split-screen mode (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC080: Verify orientation lock (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC081: Verify app on Android 11 (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC082: Verify app on Android 13 (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC083: Verify app on small screen device (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC084: Verify split-screen mode (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC085: Verify orientation lock (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC086: Verify app on Android 11 (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC087: Verify app on Android 13 (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC088: Verify app on small screen device (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC089: Verify split-screen mode (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC090: Verify orientation lock (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC091: Verify app on Android 11 (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC092: Verify app on Android 13 (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC093: Verify app on small screen device (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC094: Verify split-screen mode (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC095: Verify orientation lock (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC096: Verify app on Android 11 (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC097: Verify app on Android 13 (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC098: Verify app on small screen device (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC099: Verify split-screen mode (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC100: Verify orientation lock (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC101: Verify app on Android 11 (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC102: Verify app on Android 13 (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC103: Verify app on small screen device (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC104: Verify split-screen mode (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC105: Verify orientation lock (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC106: Verify app on Android 11 (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC107: Verify app on Android 13 (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC108: Verify app on small screen device (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC109: Verify split-screen mode (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC110: Verify orientation lock (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC111: Verify app on Android 11 (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC112: Verify app on Android 13 (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC113: Verify app on small screen device (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC114: Verify split-screen mode (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC115: Verify orientation lock (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC116: Verify app on Android 11 (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC117: Verify app on Android 13 (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC118: Verify app on small screen device (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC119: Verify split-screen mode (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC120: Verify orientation lock (Scenario 12)</t>
+  </si>
+  <si>
+    <t>App Performance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC121: Measure cold start launch time </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC122: Verify memory usage during scroll </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC123: Measure battery drain over 1 hr </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC124: Verify background CPU usage </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC125: Verify local storage cache size </t>
+  </si>
+  <si>
+    <t>TC126: Measure cold start launch time (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC127: Verify memory usage during scroll (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC128: Measure battery drain over 1 hr (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC129: Verify background CPU usage (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC130: Verify local storage cache size (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC131: Measure cold start launch time (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC132: Verify memory usage during scroll (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC133: Measure battery drain over 1 hr (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC134: Verify background CPU usage (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC135: Verify local storage cache size (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC136: Measure cold start launch time (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC137: Verify memory usage during scroll (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC138: Measure battery drain over 1 hr (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC139: Verify background CPU usage (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC140: Verify local storage cache size (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC141: Measure cold start launch time (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC142: Verify memory usage during scroll (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC143: Measure battery drain over 1 hr (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC144: Verify background CPU usage (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC145: Verify local storage cache size (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC146: Measure cold start launch time (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC147: Verify memory usage during scroll (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC148: Measure battery drain over 1 hr (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC149: Verify background CPU usage (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC150: Verify local storage cache size (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC151: Measure cold start launch time (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC152: Verify memory usage during scroll (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC153: Measure battery drain over 1 hr (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC154: Verify background CPU usage (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC155: Verify local storage cache size (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC156: Measure cold start launch time (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC157: Verify memory usage during scroll (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC158: Measure battery drain over 1 hr (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC159: Verify background CPU usage (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC160: Verify local storage cache size (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC161: Measure cold start launch time (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC162: Verify memory usage during scroll (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC163: Measure battery drain over 1 hr (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC164: Verify background CPU usage (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC165: Verify local storage cache size (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC166: Measure cold start launch time (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC167: Verify memory usage during scroll (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC168: Measure battery drain over 1 hr (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC169: Verify background CPU usage (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC170: Verify local storage cache size (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC171: Measure cold start launch time (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC172: Verify memory usage during scroll (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC173: Measure battery drain over 1 hr (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC174: Verify background CPU usage (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC175: Verify local storage cache size (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC176: Measure cold start launch time (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC177: Verify memory usage during scroll (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC178: Measure battery drain over 1 hr (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC179: Verify background CPU usage (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC180: Verify local storage cache size (Scenario 12)</t>
+  </si>
+  <si>
+    <t>Mobile Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC181: Verify biometric face unlock </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC182: Verify fingerprint auth </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC183: Verify Rooted device detection </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC184: Verify ADB backup disabled </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC185: Verify Secure storage (Keystore) </t>
+  </si>
+  <si>
+    <t>TC186: Verify biometric face unlock (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC187: Verify fingerprint auth (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC188: Verify Rooted device detection (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC189: Verify ADB backup disabled (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC190: Verify Secure storage (Keystore) (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC191: Verify biometric face unlock (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC192: Verify fingerprint auth (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC193: Verify Rooted device detection (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC194: Verify ADB backup disabled (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC195: Verify Secure storage (Keystore) (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC196: Verify biometric face unlock (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC197: Verify fingerprint auth (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC198: Verify Rooted device detection (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC199: Verify ADB backup disabled (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC200: Verify Secure storage (Keystore) (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC201: Verify biometric face unlock (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC202: Verify fingerprint auth (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC203: Verify Rooted device detection (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC204: Verify ADB backup disabled (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC205: Verify Secure storage (Keystore) (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC206: Verify biometric face unlock (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC207: Verify fingerprint auth (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC208: Verify Rooted device detection (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC209: Verify ADB backup disabled (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC210: Verify Secure storage (Keystore) (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC211: Verify biometric face unlock (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC212: Verify fingerprint auth (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC213: Verify Rooted device detection (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC214: Verify ADB backup disabled (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC215: Verify Secure storage (Keystore) (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC216: Verify biometric face unlock (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC217: Verify fingerprint auth (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC218: Verify Rooted device detection (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC219: Verify ADB backup disabled (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC220: Verify Secure storage (Keystore) (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC221: Verify biometric face unlock (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC222: Verify fingerprint auth (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC223: Verify Rooted device detection (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC224: Verify ADB backup disabled (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC225: Verify Secure storage (Keystore) (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC226: Verify biometric face unlock (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC227: Verify fingerprint auth (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC228: Verify Rooted device detection (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC229: Verify ADB backup disabled (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC230: Verify Secure storage (Keystore) (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC231: Verify biometric face unlock (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC232: Verify fingerprint auth (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC233: Verify Rooted device detection (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC234: Verify ADB backup disabled (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC235: Verify Secure storage (Keystore) (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC236: Verify biometric face unlock (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC237: Verify fingerprint auth (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC238: Verify Rooted device detection (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC239: Verify ADB backup disabled (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC240: Verify Secure storage (Keystore) (Scenario 12)</t>
+  </si>
+  <si>
+    <t>Android Integrations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC241: Verify push notifications click </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC242: Verify camera intent </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC243: Verify location GPS tracking </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC244: Verify offline mode sync </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC245: Verify Google Pay integration </t>
+  </si>
+  <si>
+    <t>TC246: Verify push notifications click (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC247: Verify camera intent (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC248: Verify location GPS tracking (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC249: Verify offline mode sync (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC250: Verify Google Pay integration (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC251: Verify push notifications click (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC252: Verify camera intent (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC253: Verify location GPS tracking (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC254: Verify offline mode sync (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC255: Verify Google Pay integration (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC256: Verify push notifications click (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC257: Verify camera intent (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC258: Verify location GPS tracking (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC259: Verify offline mode sync (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC260: Verify Google Pay integration (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC261: Verify push notifications click (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC262: Verify camera intent (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC263: Verify location GPS tracking (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC264: Verify offline mode sync (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC265: Verify Google Pay integration (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC266: Verify push notifications click (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC267: Verify camera intent (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC268: Verify location GPS tracking (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC269: Verify offline mode sync (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC270: Verify Google Pay integration (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC271: Verify push notifications click (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC272: Verify camera intent (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC273: Verify location GPS tracking (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC274: Verify offline mode sync (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC275: Verify Google Pay integration (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC276: Verify push notifications click (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC277: Verify camera intent (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC278: Verify location GPS tracking (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC279: Verify offline mode sync (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC280: Verify Google Pay integration (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC281: Verify push notifications click (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC282: Verify camera intent (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC283: Verify location GPS tracking (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC284: Verify offline mode sync (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC285: Verify Google Pay integration (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC286: Verify push notifications click (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC287: Verify camera intent (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC288: Verify location GPS tracking (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC289: Verify offline mode sync (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC290: Verify Google Pay integration (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC291: Verify push notifications click (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC292: Verify camera intent (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC293: Verify location GPS tracking (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC294: Verify offline mode sync (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC295: Verify Google Pay integration (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC296: Verify push notifications click (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC297: Verify camera intent (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC298: Verify location GPS tracking (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC299: Verify offline mode sync (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC300: Verify Google Pay integration (Scenario 12)</t>
   </si>
 </sst>
 </file>
@@ -1001,17 +1001,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0FFF0"/>
+        <fgColor rgb="FFFFE4E1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6E6FA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF0F8FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC0CB"/>
       </patternFill>
     </fill>
   </fills>

--- a/appium-android-report.xlsx
+++ b/appium-android-report.xlsx
@@ -31,10 +31,10 @@
     <t>Timestamp</t>
   </si>
   <si>
-    <t>Mobile UI/UX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC001: Verify touch target sizes </t>
+    <t>Mobile App UI/UX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC001: Verify MAHIQ splash screen loads canteen logo correctly </t>
   </si>
   <si>
     <t>PASS</t>
@@ -43,916 +43,916 @@
     <t/>
   </si>
   <si>
-    <t>8/7/2026, 4:01:40 AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC002: Verify bottom navigation bar </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC003: Verify gesture controls </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC004: Verify dark mode UI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC005: Verify splash screen animations </t>
-  </si>
-  <si>
-    <t>TC006: Verify touch target sizes (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC007: Verify bottom navigation bar (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC008: Verify gesture controls (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC009: Verify dark mode UI (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC010: Verify splash screen animations (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC011: Verify touch target sizes (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC012: Verify bottom navigation bar (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC013: Verify gesture controls (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC014: Verify dark mode UI (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC015: Verify splash screen animations (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC016: Verify touch target sizes (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC017: Verify bottom navigation bar (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC018: Verify gesture controls (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC019: Verify dark mode UI (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC020: Verify splash screen animations (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC021: Verify touch target sizes (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC022: Verify bottom navigation bar (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC023: Verify gesture controls (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC024: Verify dark mode UI (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC025: Verify splash screen animations (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC026: Verify touch target sizes (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC027: Verify bottom navigation bar (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC028: Verify gesture controls (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC029: Verify dark mode UI (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC030: Verify splash screen animations (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC031: Verify touch target sizes (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC032: Verify bottom navigation bar (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC033: Verify gesture controls (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC034: Verify dark mode UI (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC035: Verify splash screen animations (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC036: Verify touch target sizes (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC037: Verify bottom navigation bar (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC038: Verify gesture controls (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC039: Verify dark mode UI (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC040: Verify splash screen animations (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC041: Verify touch target sizes (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC042: Verify bottom navigation bar (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC043: Verify gesture controls (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC044: Verify dark mode UI (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC045: Verify splash screen animations (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC046: Verify touch target sizes (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC047: Verify bottom navigation bar (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC048: Verify gesture controls (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC049: Verify dark mode UI (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC050: Verify splash screen animations (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC051: Verify touch target sizes (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC052: Verify bottom navigation bar (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC053: Verify gesture controls (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC054: Verify dark mode UI (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC055: Verify splash screen animations (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC056: Verify touch target sizes (Scenario 12)</t>
-  </si>
-  <si>
-    <t>TC057: Verify bottom navigation bar (Scenario 12)</t>
-  </si>
-  <si>
-    <t>TC058: Verify gesture controls (Scenario 12)</t>
-  </si>
-  <si>
-    <t>TC059: Verify dark mode UI (Scenario 12)</t>
-  </si>
-  <si>
-    <t>TC060: Verify splash screen animations (Scenario 12)</t>
-  </si>
-  <si>
-    <t>Android Compatibility</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC061: Verify app on Android 11 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC062: Verify app on Android 13 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC063: Verify app on small screen device </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC064: Verify split-screen mode </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC065: Verify orientation lock </t>
-  </si>
-  <si>
-    <t>TC066: Verify app on Android 11 (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC067: Verify app on Android 13 (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC068: Verify app on small screen device (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC069: Verify split-screen mode (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC070: Verify orientation lock (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC071: Verify app on Android 11 (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC072: Verify app on Android 13 (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC073: Verify app on small screen device (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC074: Verify split-screen mode (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC075: Verify orientation lock (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC076: Verify app on Android 11 (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC077: Verify app on Android 13 (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC078: Verify app on small screen device (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC079: Verify split-screen mode (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC080: Verify orientation lock (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC081: Verify app on Android 11 (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC082: Verify app on Android 13 (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC083: Verify app on small screen device (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC084: Verify split-screen mode (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC085: Verify orientation lock (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC086: Verify app on Android 11 (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC087: Verify app on Android 13 (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC088: Verify app on small screen device (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC089: Verify split-screen mode (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC090: Verify orientation lock (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC091: Verify app on Android 11 (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC092: Verify app on Android 13 (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC093: Verify app on small screen device (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC094: Verify split-screen mode (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC095: Verify orientation lock (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC096: Verify app on Android 11 (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC097: Verify app on Android 13 (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC098: Verify app on small screen device (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC099: Verify split-screen mode (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC100: Verify orientation lock (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC101: Verify app on Android 11 (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC102: Verify app on Android 13 (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC103: Verify app on small screen device (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC104: Verify split-screen mode (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC105: Verify orientation lock (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC106: Verify app on Android 11 (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC107: Verify app on Android 13 (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC108: Verify app on small screen device (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC109: Verify split-screen mode (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC110: Verify orientation lock (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC111: Verify app on Android 11 (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC112: Verify app on Android 13 (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC113: Verify app on small screen device (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC114: Verify split-screen mode (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC115: Verify orientation lock (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC116: Verify app on Android 11 (Scenario 12)</t>
-  </si>
-  <si>
-    <t>TC117: Verify app on Android 13 (Scenario 12)</t>
-  </si>
-  <si>
-    <t>TC118: Verify app on small screen device (Scenario 12)</t>
-  </si>
-  <si>
-    <t>TC119: Verify split-screen mode (Scenario 12)</t>
-  </si>
-  <si>
-    <t>TC120: Verify orientation lock (Scenario 12)</t>
-  </si>
-  <si>
-    <t>App Performance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC121: Measure cold start launch time </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC122: Verify memory usage during scroll </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC123: Measure battery drain over 1 hr </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC124: Verify background CPU usage </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC125: Verify local storage cache size </t>
-  </si>
-  <si>
-    <t>TC126: Measure cold start launch time (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC127: Verify memory usage during scroll (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC128: Measure battery drain over 1 hr (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC129: Verify background CPU usage (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC130: Verify local storage cache size (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC131: Measure cold start launch time (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC132: Verify memory usage during scroll (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC133: Measure battery drain over 1 hr (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC134: Verify background CPU usage (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC135: Verify local storage cache size (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC136: Measure cold start launch time (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC137: Verify memory usage during scroll (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC138: Measure battery drain over 1 hr (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC139: Verify background CPU usage (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC140: Verify local storage cache size (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC141: Measure cold start launch time (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC142: Verify memory usage during scroll (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC143: Measure battery drain over 1 hr (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC144: Verify background CPU usage (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC145: Verify local storage cache size (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC146: Measure cold start launch time (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC147: Verify memory usage during scroll (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC148: Measure battery drain over 1 hr (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC149: Verify background CPU usage (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC150: Verify local storage cache size (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC151: Measure cold start launch time (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC152: Verify memory usage during scroll (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC153: Measure battery drain over 1 hr (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC154: Verify background CPU usage (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC155: Verify local storage cache size (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC156: Measure cold start launch time (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC157: Verify memory usage during scroll (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC158: Measure battery drain over 1 hr (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC159: Verify background CPU usage (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC160: Verify local storage cache size (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC161: Measure cold start launch time (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC162: Verify memory usage during scroll (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC163: Measure battery drain over 1 hr (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC164: Verify background CPU usage (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC165: Verify local storage cache size (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC166: Measure cold start launch time (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC167: Verify memory usage during scroll (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC168: Measure battery drain over 1 hr (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC169: Verify background CPU usage (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC170: Verify local storage cache size (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC171: Measure cold start launch time (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC172: Verify memory usage during scroll (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC173: Measure battery drain over 1 hr (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC174: Verify background CPU usage (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC175: Verify local storage cache size (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC176: Measure cold start launch time (Scenario 12)</t>
-  </si>
-  <si>
-    <t>TC177: Verify memory usage during scroll (Scenario 12)</t>
-  </si>
-  <si>
-    <t>TC178: Measure battery drain over 1 hr (Scenario 12)</t>
-  </si>
-  <si>
-    <t>TC179: Verify background CPU usage (Scenario 12)</t>
-  </si>
-  <si>
-    <t>TC180: Verify local storage cache size (Scenario 12)</t>
+    <t>8/7/2026, 4:12:19 AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC002: Verify dark mode UI for late-night hostel orders </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC003: Verify smooth scrolling on long canteen menu list </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC004: Verify 'Add to Cart' floating button animation </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC005: Verify readable fonts for food item descriptions </t>
+  </si>
+  <si>
+    <t>TC006: Verify MAHIQ splash screen loads canteen logo correctly (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC007: Verify dark mode UI for late-night hostel orders (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC008: Verify smooth scrolling on long canteen menu list (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC009: Verify 'Add to Cart' floating button animation (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC010: Verify readable fonts for food item descriptions (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC011: Verify MAHIQ splash screen loads canteen logo correctly (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC012: Verify dark mode UI for late-night hostel orders (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC013: Verify smooth scrolling on long canteen menu list (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC014: Verify 'Add to Cart' floating button animation (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC015: Verify readable fonts for food item descriptions (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC016: Verify MAHIQ splash screen loads canteen logo correctly (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC017: Verify dark mode UI for late-night hostel orders (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC018: Verify smooth scrolling on long canteen menu list (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC019: Verify 'Add to Cart' floating button animation (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC020: Verify readable fonts for food item descriptions (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC021: Verify MAHIQ splash screen loads canteen logo correctly (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC022: Verify dark mode UI for late-night hostel orders (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC023: Verify smooth scrolling on long canteen menu list (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC024: Verify 'Add to Cart' floating button animation (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC025: Verify readable fonts for food item descriptions (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC026: Verify MAHIQ splash screen loads canteen logo correctly (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC027: Verify dark mode UI for late-night hostel orders (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC028: Verify smooth scrolling on long canteen menu list (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC029: Verify 'Add to Cart' floating button animation (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC030: Verify readable fonts for food item descriptions (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC031: Verify MAHIQ splash screen loads canteen logo correctly (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC032: Verify dark mode UI for late-night hostel orders (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC033: Verify smooth scrolling on long canteen menu list (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC034: Verify 'Add to Cart' floating button animation (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC035: Verify readable fonts for food item descriptions (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC036: Verify MAHIQ splash screen loads canteen logo correctly (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC037: Verify dark mode UI for late-night hostel orders (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC038: Verify smooth scrolling on long canteen menu list (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC039: Verify 'Add to Cart' floating button animation (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC040: Verify readable fonts for food item descriptions (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC041: Verify MAHIQ splash screen loads canteen logo correctly (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC042: Verify dark mode UI for late-night hostel orders (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC043: Verify smooth scrolling on long canteen menu list (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC044: Verify 'Add to Cart' floating button animation (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC045: Verify readable fonts for food item descriptions (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC046: Verify MAHIQ splash screen loads canteen logo correctly (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC047: Verify dark mode UI for late-night hostel orders (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC048: Verify smooth scrolling on long canteen menu list (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC049: Verify 'Add to Cart' floating button animation (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC050: Verify readable fonts for food item descriptions (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC051: Verify MAHIQ splash screen loads canteen logo correctly (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC052: Verify dark mode UI for late-night hostel orders (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC053: Verify smooth scrolling on long canteen menu list (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC054: Verify 'Add to Cart' floating button animation (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC055: Verify readable fonts for food item descriptions (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC056: Verify MAHIQ splash screen loads canteen logo correctly (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC057: Verify dark mode UI for late-night hostel orders (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC058: Verify smooth scrolling on long canteen menu list (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC059: Verify 'Add to Cart' floating button animation (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC060: Verify readable fonts for food item descriptions (Scenario 12)</t>
+  </si>
+  <si>
+    <t>Canteen Core Flows</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC061: Verify adding 3 Samosas and 1 Coffee to cart </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC062: Verify cart total recalculates when item quantity changes </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC063: Verify student can apply valid coupon code at checkout </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC064: Verify Razorpay UPI payment popup launches correctly </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC065: Verify order is placed and virtual token is generated </t>
+  </si>
+  <si>
+    <t>TC066: Verify adding 3 Samosas and 1 Coffee to cart (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC067: Verify cart total recalculates when item quantity changes (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC068: Verify student can apply valid coupon code at checkout (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC069: Verify Razorpay UPI payment popup launches correctly (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC070: Verify order is placed and virtual token is generated (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC071: Verify adding 3 Samosas and 1 Coffee to cart (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC072: Verify cart total recalculates when item quantity changes (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC073: Verify student can apply valid coupon code at checkout (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC074: Verify Razorpay UPI payment popup launches correctly (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC075: Verify order is placed and virtual token is generated (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC076: Verify adding 3 Samosas and 1 Coffee to cart (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC077: Verify cart total recalculates when item quantity changes (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC078: Verify student can apply valid coupon code at checkout (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC079: Verify Razorpay UPI payment popup launches correctly (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC080: Verify order is placed and virtual token is generated (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC081: Verify adding 3 Samosas and 1 Coffee to cart (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC082: Verify cart total recalculates when item quantity changes (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC083: Verify student can apply valid coupon code at checkout (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC084: Verify Razorpay UPI payment popup launches correctly (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC085: Verify order is placed and virtual token is generated (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC086: Verify adding 3 Samosas and 1 Coffee to cart (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC087: Verify cart total recalculates when item quantity changes (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC088: Verify student can apply valid coupon code at checkout (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC089: Verify Razorpay UPI payment popup launches correctly (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC090: Verify order is placed and virtual token is generated (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC091: Verify adding 3 Samosas and 1 Coffee to cart (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC092: Verify cart total recalculates when item quantity changes (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC093: Verify student can apply valid coupon code at checkout (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC094: Verify Razorpay UPI payment popup launches correctly (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC095: Verify order is placed and virtual token is generated (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC096: Verify adding 3 Samosas and 1 Coffee to cart (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC097: Verify cart total recalculates when item quantity changes (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC098: Verify student can apply valid coupon code at checkout (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC099: Verify Razorpay UPI payment popup launches correctly (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC100: Verify order is placed and virtual token is generated (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC101: Verify adding 3 Samosas and 1 Coffee to cart (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC102: Verify cart total recalculates when item quantity changes (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC103: Verify student can apply valid coupon code at checkout (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC104: Verify Razorpay UPI payment popup launches correctly (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC105: Verify order is placed and virtual token is generated (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC106: Verify adding 3 Samosas and 1 Coffee to cart (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC107: Verify cart total recalculates when item quantity changes (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC108: Verify student can apply valid coupon code at checkout (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC109: Verify Razorpay UPI payment popup launches correctly (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC110: Verify order is placed and virtual token is generated (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC111: Verify adding 3 Samosas and 1 Coffee to cart (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC112: Verify cart total recalculates when item quantity changes (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC113: Verify student can apply valid coupon code at checkout (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC114: Verify Razorpay UPI payment popup launches correctly (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC115: Verify order is placed and virtual token is generated (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC116: Verify adding 3 Samosas and 1 Coffee to cart (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC117: Verify cart total recalculates when item quantity changes (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC118: Verify student can apply valid coupon code at checkout (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC119: Verify Razorpay UPI payment popup launches correctly (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC120: Verify order is placed and virtual token is generated (Scenario 12)</t>
+  </si>
+  <si>
+    <t>Queue &amp; Tracking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC121: Verify real-time queue length shows 'High Traffic' </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC122: Verify order status changes to 'Preparing' live </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC123: Verify estimated wait time updates dynamically </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC124: Verify push notification received when order is 'Ready' </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC125: Verify past orders appear in student order history </t>
+  </si>
+  <si>
+    <t>TC126: Verify real-time queue length shows 'High Traffic' (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC127: Verify order status changes to 'Preparing' live (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC128: Verify estimated wait time updates dynamically (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC129: Verify push notification received when order is 'Ready' (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC130: Verify past orders appear in student order history (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC131: Verify real-time queue length shows 'High Traffic' (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC132: Verify order status changes to 'Preparing' live (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC133: Verify estimated wait time updates dynamically (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC134: Verify push notification received when order is 'Ready' (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC135: Verify past orders appear in student order history (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC136: Verify real-time queue length shows 'High Traffic' (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC137: Verify order status changes to 'Preparing' live (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC138: Verify estimated wait time updates dynamically (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC139: Verify push notification received when order is 'Ready' (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC140: Verify past orders appear in student order history (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC141: Verify real-time queue length shows 'High Traffic' (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC142: Verify order status changes to 'Preparing' live (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC143: Verify estimated wait time updates dynamically (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC144: Verify push notification received when order is 'Ready' (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC145: Verify past orders appear in student order history (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC146: Verify real-time queue length shows 'High Traffic' (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC147: Verify order status changes to 'Preparing' live (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC148: Verify estimated wait time updates dynamically (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC149: Verify push notification received when order is 'Ready' (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC150: Verify past orders appear in student order history (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC151: Verify real-time queue length shows 'High Traffic' (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC152: Verify order status changes to 'Preparing' live (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC153: Verify estimated wait time updates dynamically (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC154: Verify push notification received when order is 'Ready' (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC155: Verify past orders appear in student order history (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC156: Verify real-time queue length shows 'High Traffic' (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC157: Verify order status changes to 'Preparing' live (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC158: Verify estimated wait time updates dynamically (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC159: Verify push notification received when order is 'Ready' (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC160: Verify past orders appear in student order history (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC161: Verify real-time queue length shows 'High Traffic' (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC162: Verify order status changes to 'Preparing' live (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC163: Verify estimated wait time updates dynamically (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC164: Verify push notification received when order is 'Ready' (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC165: Verify past orders appear in student order history (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC166: Verify real-time queue length shows 'High Traffic' (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC167: Verify order status changes to 'Preparing' live (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC168: Verify estimated wait time updates dynamically (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC169: Verify push notification received when order is 'Ready' (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC170: Verify past orders appear in student order history (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC171: Verify real-time queue length shows 'High Traffic' (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC172: Verify order status changes to 'Preparing' live (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC173: Verify estimated wait time updates dynamically (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC174: Verify push notification received when order is 'Ready' (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC175: Verify past orders appear in student order history (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC176: Verify real-time queue length shows 'High Traffic' (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC177: Verify order status changes to 'Preparing' live (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC178: Verify estimated wait time updates dynamically (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC179: Verify push notification received when order is 'Ready' (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC180: Verify past orders appear in student order history (Scenario 12)</t>
   </si>
   <si>
     <t>Mobile Security</t>
   </si>
   <si>
-    <t xml:space="preserve">TC181: Verify biometric face unlock </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC182: Verify fingerprint auth </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC183: Verify Rooted device detection </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC184: Verify ADB backup disabled </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC185: Verify Secure storage (Keystore) </t>
-  </si>
-  <si>
-    <t>TC186: Verify biometric face unlock (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC187: Verify fingerprint auth (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC188: Verify Rooted device detection (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC189: Verify ADB backup disabled (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC190: Verify Secure storage (Keystore) (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC191: Verify biometric face unlock (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC192: Verify fingerprint auth (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC193: Verify Rooted device detection (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC194: Verify ADB backup disabled (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC195: Verify Secure storage (Keystore) (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC196: Verify biometric face unlock (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC197: Verify fingerprint auth (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC198: Verify Rooted device detection (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC199: Verify ADB backup disabled (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC200: Verify Secure storage (Keystore) (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC201: Verify biometric face unlock (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC202: Verify fingerprint auth (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC203: Verify Rooted device detection (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC204: Verify ADB backup disabled (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC205: Verify Secure storage (Keystore) (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC206: Verify biometric face unlock (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC207: Verify fingerprint auth (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC208: Verify Rooted device detection (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC209: Verify ADB backup disabled (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC210: Verify Secure storage (Keystore) (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC211: Verify biometric face unlock (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC212: Verify fingerprint auth (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC213: Verify Rooted device detection (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC214: Verify ADB backup disabled (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC215: Verify Secure storage (Keystore) (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC216: Verify biometric face unlock (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC217: Verify fingerprint auth (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC218: Verify Rooted device detection (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC219: Verify ADB backup disabled (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC220: Verify Secure storage (Keystore) (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC221: Verify biometric face unlock (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC222: Verify fingerprint auth (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC223: Verify Rooted device detection (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC224: Verify ADB backup disabled (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC225: Verify Secure storage (Keystore) (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC226: Verify biometric face unlock (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC227: Verify fingerprint auth (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC228: Verify Rooted device detection (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC229: Verify ADB backup disabled (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC230: Verify Secure storage (Keystore) (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC231: Verify biometric face unlock (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC232: Verify fingerprint auth (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC233: Verify Rooted device detection (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC234: Verify ADB backup disabled (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC235: Verify Secure storage (Keystore) (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC236: Verify biometric face unlock (Scenario 12)</t>
-  </si>
-  <si>
-    <t>TC237: Verify fingerprint auth (Scenario 12)</t>
-  </si>
-  <si>
-    <t>TC238: Verify Rooted device detection (Scenario 12)</t>
-  </si>
-  <si>
-    <t>TC239: Verify ADB backup disabled (Scenario 12)</t>
-  </si>
-  <si>
-    <t>TC240: Verify Secure storage (Keystore) (Scenario 12)</t>
-  </si>
-  <si>
-    <t>Android Integrations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC241: Verify push notifications click </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC242: Verify camera intent </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC243: Verify location GPS tracking </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC244: Verify offline mode sync </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC245: Verify Google Pay integration </t>
-  </si>
-  <si>
-    <t>TC246: Verify push notifications click (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC247: Verify camera intent (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC248: Verify location GPS tracking (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC249: Verify offline mode sync (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC250: Verify Google Pay integration (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC251: Verify push notifications click (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC252: Verify camera intent (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC253: Verify location GPS tracking (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC254: Verify offline mode sync (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC255: Verify Google Pay integration (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC256: Verify push notifications click (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC257: Verify camera intent (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC258: Verify location GPS tracking (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC259: Verify offline mode sync (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC260: Verify Google Pay integration (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC261: Verify push notifications click (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC262: Verify camera intent (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC263: Verify location GPS tracking (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC264: Verify offline mode sync (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC265: Verify Google Pay integration (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC266: Verify push notifications click (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC267: Verify camera intent (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC268: Verify location GPS tracking (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC269: Verify offline mode sync (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC270: Verify Google Pay integration (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC271: Verify push notifications click (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC272: Verify camera intent (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC273: Verify location GPS tracking (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC274: Verify offline mode sync (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC275: Verify Google Pay integration (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC276: Verify push notifications click (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC277: Verify camera intent (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC278: Verify location GPS tracking (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC279: Verify offline mode sync (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC280: Verify Google Pay integration (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC281: Verify push notifications click (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC282: Verify camera intent (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC283: Verify location GPS tracking (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC284: Verify offline mode sync (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC285: Verify Google Pay integration (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC286: Verify push notifications click (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC287: Verify camera intent (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC288: Verify location GPS tracking (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC289: Verify offline mode sync (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC290: Verify Google Pay integration (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC291: Verify push notifications click (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC292: Verify camera intent (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC293: Verify location GPS tracking (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC294: Verify offline mode sync (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC295: Verify Google Pay integration (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC296: Verify push notifications click (Scenario 12)</t>
-  </si>
-  <si>
-    <t>TC297: Verify camera intent (Scenario 12)</t>
-  </si>
-  <si>
-    <t>TC298: Verify location GPS tracking (Scenario 12)</t>
-  </si>
-  <si>
-    <t>TC299: Verify offline mode sync (Scenario 12)</t>
-  </si>
-  <si>
-    <t>TC300: Verify Google Pay integration (Scenario 12)</t>
+    <t xml:space="preserve">TC181: Verify biometric auth for quick checkout </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC182: Verify automatic logout after 30 mins of inactivity </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC183: Verify student cannot access Admin dashboard </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC184: Verify secure transmission of payment details </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC185: Verify app prevents screen recording on payment page </t>
+  </si>
+  <si>
+    <t>TC186: Verify biometric auth for quick checkout (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC187: Verify automatic logout after 30 mins of inactivity (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC188: Verify student cannot access Admin dashboard (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC189: Verify secure transmission of payment details (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC190: Verify app prevents screen recording on payment page (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC191: Verify biometric auth for quick checkout (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC192: Verify automatic logout after 30 mins of inactivity (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC193: Verify student cannot access Admin dashboard (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC194: Verify secure transmission of payment details (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC195: Verify app prevents screen recording on payment page (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC196: Verify biometric auth for quick checkout (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC197: Verify automatic logout after 30 mins of inactivity (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC198: Verify student cannot access Admin dashboard (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC199: Verify secure transmission of payment details (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC200: Verify app prevents screen recording on payment page (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC201: Verify biometric auth for quick checkout (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC202: Verify automatic logout after 30 mins of inactivity (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC203: Verify student cannot access Admin dashboard (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC204: Verify secure transmission of payment details (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC205: Verify app prevents screen recording on payment page (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC206: Verify biometric auth for quick checkout (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC207: Verify automatic logout after 30 mins of inactivity (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC208: Verify student cannot access Admin dashboard (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC209: Verify secure transmission of payment details (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC210: Verify app prevents screen recording on payment page (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC211: Verify biometric auth for quick checkout (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC212: Verify automatic logout after 30 mins of inactivity (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC213: Verify student cannot access Admin dashboard (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC214: Verify secure transmission of payment details (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC215: Verify app prevents screen recording on payment page (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC216: Verify biometric auth for quick checkout (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC217: Verify automatic logout after 30 mins of inactivity (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC218: Verify student cannot access Admin dashboard (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC219: Verify secure transmission of payment details (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC220: Verify app prevents screen recording on payment page (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC221: Verify biometric auth for quick checkout (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC222: Verify automatic logout after 30 mins of inactivity (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC223: Verify student cannot access Admin dashboard (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC224: Verify secure transmission of payment details (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC225: Verify app prevents screen recording on payment page (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC226: Verify biometric auth for quick checkout (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC227: Verify automatic logout after 30 mins of inactivity (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC228: Verify student cannot access Admin dashboard (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC229: Verify secure transmission of payment details (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC230: Verify app prevents screen recording on payment page (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC231: Verify biometric auth for quick checkout (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC232: Verify automatic logout after 30 mins of inactivity (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC233: Verify student cannot access Admin dashboard (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC234: Verify secure transmission of payment details (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC235: Verify app prevents screen recording on payment page (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC236: Verify biometric auth for quick checkout (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC237: Verify automatic logout after 30 mins of inactivity (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC238: Verify student cannot access Admin dashboard (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC239: Verify secure transmission of payment details (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC240: Verify app prevents screen recording on payment page (Scenario 12)</t>
+  </si>
+  <si>
+    <t>Hardware Integrations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC241: Verify scanning table QR code opens menu directly </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC242: Verify GPS location warns if outside college campus </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC243: Verify push notification sound for order readiness </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC244: Verify background sync updates menu prices </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC245: Verify camera intent for profile picture upload </t>
+  </si>
+  <si>
+    <t>TC246: Verify scanning table QR code opens menu directly (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC247: Verify GPS location warns if outside college campus (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC248: Verify push notification sound for order readiness (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC249: Verify background sync updates menu prices (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC250: Verify camera intent for profile picture upload (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC251: Verify scanning table QR code opens menu directly (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC252: Verify GPS location warns if outside college campus (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC253: Verify push notification sound for order readiness (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC254: Verify background sync updates menu prices (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC255: Verify camera intent for profile picture upload (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC256: Verify scanning table QR code opens menu directly (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC257: Verify GPS location warns if outside college campus (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC258: Verify push notification sound for order readiness (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC259: Verify background sync updates menu prices (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC260: Verify camera intent for profile picture upload (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC261: Verify scanning table QR code opens menu directly (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC262: Verify GPS location warns if outside college campus (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC263: Verify push notification sound for order readiness (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC264: Verify background sync updates menu prices (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC265: Verify camera intent for profile picture upload (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC266: Verify scanning table QR code opens menu directly (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC267: Verify GPS location warns if outside college campus (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC268: Verify push notification sound for order readiness (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC269: Verify background sync updates menu prices (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC270: Verify camera intent for profile picture upload (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC271: Verify scanning table QR code opens menu directly (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC272: Verify GPS location warns if outside college campus (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC273: Verify push notification sound for order readiness (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC274: Verify background sync updates menu prices (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC275: Verify camera intent for profile picture upload (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC276: Verify scanning table QR code opens menu directly (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC277: Verify GPS location warns if outside college campus (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC278: Verify push notification sound for order readiness (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC279: Verify background sync updates menu prices (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC280: Verify camera intent for profile picture upload (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC281: Verify scanning table QR code opens menu directly (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC282: Verify GPS location warns if outside college campus (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC283: Verify push notification sound for order readiness (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC284: Verify background sync updates menu prices (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC285: Verify camera intent for profile picture upload (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC286: Verify scanning table QR code opens menu directly (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC287: Verify GPS location warns if outside college campus (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC288: Verify push notification sound for order readiness (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC289: Verify background sync updates menu prices (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC290: Verify camera intent for profile picture upload (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC291: Verify scanning table QR code opens menu directly (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC292: Verify GPS location warns if outside college campus (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC293: Verify push notification sound for order readiness (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC294: Verify background sync updates menu prices (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC295: Verify camera intent for profile picture upload (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC296: Verify scanning table QR code opens menu directly (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC297: Verify GPS location warns if outside college campus (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC298: Verify push notification sound for order readiness (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC299: Verify background sync updates menu prices (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC300: Verify camera intent for profile picture upload (Scenario 12)</t>
   </si>
 </sst>
 </file>

--- a/appium-android-report.xlsx
+++ b/appium-android-report.xlsx
@@ -43,7 +43,7 @@
     <t/>
   </si>
   <si>
-    <t>8/7/2026, 4:12:19 AM</t>
+    <t>8/7/2026, 5:03:51 AM</t>
   </si>
   <si>
     <t xml:space="preserve">TC002: Verify dark mode UI for late-night hostel orders </t>

--- a/appium-android-report.xlsx
+++ b/appium-android-report.xlsx
@@ -43,7 +43,7 @@
     <t/>
   </si>
   <si>
-    <t>8/7/2026, 5:03:51 AM</t>
+    <t>8/7/2026, 5:11:55 AM</t>
   </si>
   <si>
     <t xml:space="preserve">TC002: Verify dark mode UI for late-night hostel orders </t>

--- a/appium-android-report.xlsx
+++ b/appium-android-report.xlsx
@@ -43,7 +43,7 @@
     <t/>
   </si>
   <si>
-    <t>8/7/2026, 5:11:55 AM</t>
+    <t>8/7/2026, 5:18:18 AM</t>
   </si>
   <si>
     <t xml:space="preserve">TC002: Verify dark mode UI for late-night hostel orders </t>

--- a/appium-android-report.xlsx
+++ b/appium-android-report.xlsx
@@ -43,7 +43,7 @@
     <t/>
   </si>
   <si>
-    <t>8/7/2026, 5:18:18 AM</t>
+    <t>8/7/2026, 5:20:04 AM</t>
   </si>
   <si>
     <t xml:space="preserve">TC002: Verify dark mode UI for late-night hostel orders </t>

--- a/appium-android-report.xlsx
+++ b/appium-android-report.xlsx
@@ -43,7 +43,7 @@
     <t/>
   </si>
   <si>
-    <t>8/7/2026, 5:20:04 AM</t>
+    <t>8/7/2026, 5:31:57 AM</t>
   </si>
   <si>
     <t xml:space="preserve">TC002: Verify dark mode UI for late-night hostel orders </t>

--- a/appium-android-report.xlsx
+++ b/appium-android-report.xlsx
@@ -43,7 +43,7 @@
     <t/>
   </si>
   <si>
-    <t>8/7/2026, 5:31:57 AM</t>
+    <t>8/7/2026, 5:38:04 AM</t>
   </si>
   <si>
     <t xml:space="preserve">TC002: Verify dark mode UI for late-night hostel orders </t>

--- a/appium-android-report.xlsx
+++ b/appium-android-report.xlsx
@@ -43,7 +43,7 @@
     <t/>
   </si>
   <si>
-    <t>8/7/2026, 5:38:04 AM</t>
+    <t>8/7/2026, 5:45:09 AM</t>
   </si>
   <si>
     <t xml:space="preserve">TC002: Verify dark mode UI for late-night hostel orders </t>

--- a/appium-android-report.xlsx
+++ b/appium-android-report.xlsx
@@ -43,7 +43,7 @@
     <t/>
   </si>
   <si>
-    <t>8/7/2026, 5:45:09 AM</t>
+    <t>8/7/2026, 5:55:52 AM</t>
   </si>
   <si>
     <t xml:space="preserve">TC002: Verify dark mode UI for late-night hostel orders </t>

--- a/appium-android-report.xlsx
+++ b/appium-android-report.xlsx
@@ -43,7 +43,7 @@
     <t/>
   </si>
   <si>
-    <t>8/7/2026, 5:55:52 AM</t>
+    <t>8/7/2026, 6:14:44 AM</t>
   </si>
   <si>
     <t xml:space="preserve">TC002: Verify dark mode UI for late-night hostel orders </t>

--- a/appium-android-report.xlsx
+++ b/appium-android-report.xlsx
@@ -43,7 +43,7 @@
     <t/>
   </si>
   <si>
-    <t>8/7/2026, 6:14:44 AM</t>
+    <t>8/7/2026, 6:20:07 AM</t>
   </si>
   <si>
     <t xml:space="preserve">TC002: Verify dark mode UI for late-night hostel orders </t>

--- a/appium-android-report.xlsx
+++ b/appium-android-report.xlsx
@@ -43,7 +43,7 @@
     <t/>
   </si>
   <si>
-    <t>8/7/2026, 6:20:07 AM</t>
+    <t>8/7/2026, 6:30:06 AM</t>
   </si>
   <si>
     <t xml:space="preserve">TC002: Verify dark mode UI for late-night hostel orders </t>
